--- a/src/attributions/attributions_ig_traj_172.xlsx
+++ b/src/attributions/attributions_ig_traj_172.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2493262131321044</v>
+        <v>0.09668886637061896</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09047041967019012</v>
+        <v>-0.04691763020137454</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005007437087639604</v>
+        <v>-0.02067784331512241</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1781781744317549</v>
+        <v>0.09590112497364216</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08297812254876046</v>
+        <v>-0.0538685338684148</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.03316025022117281</v>
+        <v>-0.03509652116999055</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1056,19 +1056,19 @@
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1440744903824693</v>
+        <v>0.04357932106104383</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01103128121362423</v>
+        <v>-0.0003977598348361875</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02945133558766439</v>
+        <v>-0.03229785543485171</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
@@ -1080,52 +1080,52 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2122634876182237</v>
+        <v>-0.01300748841829029</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01467701872397577</v>
+        <v>-0.0446958209820583</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.05181857208293127</v>
+        <v>-0.02338633782352782</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0712464553638871</v>
+        <v>0.04909789122529108</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.04730772296670017</v>
+        <v>-0.003231549800953568</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06136400769167726</v>
+        <v>0.04784567309406686</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1134,52 +1134,52 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.6122835075067905</v>
+        <v>0.2502439720656899</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.05943027075250897</v>
+        <v>-0.1338915586629909</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0967602613844615</v>
+        <v>-0.04865724843191536</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.1269021236776724</v>
+        <v>-0.03469996378728873</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.1492683504143352</v>
+        <v>-0.001000548958398684</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.2105243661574064</v>
+        <v>-0.02123356265460485</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1188,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.09069393592949695</v>
+        <v>-0.04567746365955711</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.06857920815911207</v>
+        <v>0.01235442590036724</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1974344806953126</v>
+        <v>0.07826290331867533</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.172622407007552</v>
+        <v>0.09576012325368581</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.009103952041957079</v>
+        <v>-0.04957172419672228</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03039735606085702</v>
+        <v>-0.01366450936203445</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,106 +1236,106 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1444890010655884</v>
+        <v>-0.07635629256545001</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.05743363640489321</v>
+        <v>0.04385884736143492</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.04770470821978463</v>
+        <v>0.01820897275501186</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.002548818253159134</v>
+        <v>-0.0009692025654976347</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.003960982318568434</v>
+        <v>-0.001837909539690808</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.004632707577347698</v>
+        <v>7.15806689679254e-05</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1355587006098324</v>
+        <v>-0.08641431672054437</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0922449015940546</v>
+        <v>0.04716291802119487</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.03815630460543089</v>
+        <v>0.03004284195674819</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1047683893819941</v>
+        <v>-0.05340945230289066</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.07612283721339115</v>
+        <v>0.03986723228014737</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.08312856067849972</v>
+        <v>-0.08061714450786557</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1344,31 +1344,31 @@
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01661790973737876</v>
+        <v>0.05091364591380868</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.09351131533169769</v>
+        <v>0.03787218379283594</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.02386460762677996</v>
+        <v>0.02834995111015176</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1429898115530247</v>
+        <v>0.005469401401505617</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.03182074951069441</v>
+        <v>0.02513203247264189</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.02121408327053145</v>
+        <v>-0.01413134411125402</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
@@ -1407,25 +1407,25 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.09937939195826995</v>
+        <v>-0.0329893291029803</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.1034951053505888</v>
+        <v>0.02281331318944009</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.07766191348628193</v>
+        <v>0.01656888184158228</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
@@ -1434,25 +1434,25 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.1137557869795488</v>
+        <v>-0.05401229715207625</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.10575404807831</v>
+        <v>0.01990065823090504</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.06147775637444692</v>
+        <v>-0.03131385081144101</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,49 +1461,49 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1464001503017164</v>
+        <v>-0.09068632649078502</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.06796683377388016</v>
+        <v>0.04980289078788833</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.05297516906849892</v>
+        <v>0.01170447142172767</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0149451873456273</v>
+        <v>-0.06982283009132748</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.05118079571244191</v>
+        <v>-0.01387651422226986</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1354062904086601</v>
+        <v>0.08583603094586303</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN2" t="n">
         <v>-0</v>
@@ -1512,55 +1512,55 @@
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.04322461679168445</v>
+        <v>-0.05474709668687103</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1356823876548291</v>
+        <v>0.2609188329250886</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.1325069089090666</v>
+        <v>0.06877590849803397</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.009299329429261734</v>
+        <v>-0.05944235637427562</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.05782163218015451</v>
+        <v>0.02650510233512429</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1571,16 +1571,16 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.04997783771659522</v>
+        <v>-0.1867476087789716</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1676149254539349</v>
+        <v>0.1284990745777105</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06140256580887671</v>
+        <v>0.01123813250986128</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -1598,19 +1598,19 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.03942022231905946</v>
+        <v>-0.1468213861128442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1365185281754192</v>
+        <v>0.09093668648196696</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.05612976363961841</v>
+        <v>0.01725259634212458</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -1625,70 +1625,70 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09258102990290713</v>
+        <v>-0.06023516820628677</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04898703691054553</v>
+        <v>-0.04677546200252414</v>
       </c>
       <c r="V3" t="n">
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.09269915467885714</v>
+        <v>-0.0426098514697914</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1090802455734164</v>
+        <v>-0.07310594103401903</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0253716710426026</v>
+        <v>0.10765673295296</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.08865070650664492</v>
+        <v>-0.06708846116107761</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.1086136736597716</v>
+        <v>-0.2236054183560169</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1246384878444639</v>
+        <v>0.06695422143617129</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1160915356137335</v>
+        <v>-0.1907546035553783</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
@@ -1700,52 +1700,52 @@
         <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.07083077654911196</v>
+        <v>-0.3769518518820508</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3295372683671105</v>
+        <v>0.03816432700870642</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.01321895790182407</v>
+        <v>-0.02556608769792802</v>
       </c>
       <c r="AY3" t="n">
         <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
         <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.01202122288833101</v>
+        <v>0.1466404488049451</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1091337157486177</v>
+        <v>0.2230843838012836</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.02658759485845237</v>
+        <v>0.05479838758853253</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
@@ -1757,82 +1757,82 @@
         <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.005426014773549575</v>
+        <v>0.06412696924739847</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.07356766485066281</v>
+        <v>-0.03669735603007228</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.02776275308003097</v>
+        <v>0.003404103005931074</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.03498311567460751</v>
+        <v>-0.1903145241872499</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1200283752502502</v>
+        <v>0.04077804382201689</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.09040916725829239</v>
+        <v>0.02274460294160973</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.06021437619762204</v>
+        <v>0.2189580434533276</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.05051417675046541</v>
+        <v>-0.08899574430183693</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.008743696753527508</v>
+        <v>0.01562571041295415</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,16 +1841,16 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.02141520842954665</v>
+        <v>0.04403572650864229</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.00238323739104794</v>
+        <v>-0.01021112777112507</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.007504385256826003</v>
+        <v>-0.002991081744503312</v>
       </c>
       <c r="CR3" t="n">
         <v>0</v>
@@ -1859,34 +1859,34 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.04868898109280945</v>
+        <v>0.2304687757372648</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.05133964312290161</v>
+        <v>-0.08815300216829539</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.03146738791294247</v>
+        <v>0.004172603320147989</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,52 +1895,52 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.06510812253069616</v>
+        <v>0.05086083242112584</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0334113895362084</v>
+        <v>-0.05708612504292779</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.04854049943128208</v>
+        <v>0.07712152071739337</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.01508496527051603</v>
+        <v>-0.1261782685370031</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01945716684271941</v>
+        <v>-0.0615674594727189</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.05460211871061611</v>
+        <v>-0.06648649159419465</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
@@ -1949,43 +1949,43 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.01217255028135435</v>
+        <v>0.08844923837903274</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0365369651862351</v>
+        <v>0.001824184782047608</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1311385209749855</v>
+        <v>0.01061099951051765</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.02623991417174484</v>
+        <v>0.190651712375932</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.0402393476542928</v>
+        <v>0.007394648190532539</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.05259418740697912</v>
+        <v>0.02074360671771663</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
@@ -2000,55 +2000,55 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1025999897483196</v>
+        <v>0.2167457979703517</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.02335050068156914</v>
+        <v>-0.02395571588707121</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.02878953589432814</v>
+        <v>-0.01759084958189409</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.03770218618122801</v>
+        <v>0.2661897158346282</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.03298975539881078</v>
+        <v>-0.08569550302214736</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01123137441341976</v>
+        <v>-0.01217614936822015</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,19 +2057,19 @@
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.001441347648390726</v>
+        <v>0.0321045617854286</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.01865764777040516</v>
+        <v>0.1148475600787955</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.0200389846406851</v>
+        <v>0.005555405912283794</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2078,52 +2078,52 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.08984224815967368</v>
+        <v>0.1497867154237638</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.05853545012280349</v>
+        <v>0.03521608871878642</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1783506569267445</v>
+        <v>0.05926477649516307</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.06655637323533845</v>
+        <v>0.2273232400565261</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0001042885133974013</v>
+        <v>0.04609024253233515</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -3278,16 +3278,16 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4474865863520752</v>
+        <v>0.1794945476899227</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1336275900933849</v>
+        <v>-0.07602231352396674</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06725164175146832</v>
+        <v>-0.03239148704305576</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3296,25 +3296,25 @@
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2823281147805614</v>
+        <v>0.1579826463141941</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1251371444139582</v>
+        <v>-0.1089965272672736</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04870026785890304</v>
+        <v>-0.06027980385985372</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3332,76 +3332,76 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1630797882969007</v>
+        <v>0.05194633888644588</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.06915152423521755</v>
+        <v>-0.03445527949589133</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08133663112614212</v>
+        <v>-0.04929536656682268</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06848895441024379</v>
+        <v>-0.05758262893342584</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.00492108621416142</v>
+        <v>-0.1303993358786637</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05332945893223758</v>
+        <v>-0.02773651188144024</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0801020029823524</v>
+        <v>0.07480550681447666</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.08148502215507999</v>
+        <v>-0.06428065254656833</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.06123003012997424</v>
+        <v>0.0585879312971068</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3410,55 +3410,55 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.6162849687873244</v>
+        <v>0.2305427733646092</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.005255030541280045</v>
+        <v>-0.06072068647299864</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.08334796461491521</v>
+        <v>-0.1501643361378626</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1247015455009327</v>
+        <v>-0.002806818440904029</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.184827277016706</v>
+        <v>-0.0368917390192065</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.192167182361609</v>
+        <v>0.0002592659038297918</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1004192498097808</v>
+        <v>-0.00276520774148043</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1378364432021212</v>
+        <v>0.02871190610182065</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.134140268681968</v>
+        <v>0.06289832772953796</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
@@ -3488,103 +3488,103 @@
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1754867908039624</v>
+        <v>0.08516056889459851</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.02796695221143333</v>
+        <v>-0.05562012594070462</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02756639829544939</v>
+        <v>-0.02177360697870141</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1619613420840278</v>
+        <v>-0.1100779107998735</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01159253285347901</v>
+        <v>0.08878330365668227</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.02887369787882085</v>
+        <v>0.01673120253155298</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.00990840773133491</v>
+        <v>-0.01494604600930018</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.07222815664675994</v>
+        <v>0.07051491152977911</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.05101800256490115</v>
+        <v>0.0004407193001163404</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1346282216753453</v>
+        <v>-0.1140852574557767</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.06808889017224122</v>
+        <v>0.09776058843550882</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.04713275424182805</v>
+        <v>0.02654969848690822</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3596,22 +3596,22 @@
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.04539933068367116</v>
+        <v>-0.07093296950443181</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1208047118250775</v>
+        <v>0.002891847890548717</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07168752030847722</v>
+        <v>-0.08513783711738086</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
@@ -3623,25 +3623,25 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.1148323652407947</v>
+        <v>-0.06001919701735027</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.021459592425942</v>
+        <v>-0.006623986740187901</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.08549571110580072</v>
+        <v>0.001221574447842209</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,76 +3656,76 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.08952503995456616</v>
+        <v>-0.03329591853295107</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.01717339737290782</v>
+        <v>0.07745455121507816</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0177110666226803</v>
+        <v>0.02101972927282198</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1224144107696014</v>
+        <v>-0.08893810105448031</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.01437838595221091</v>
+        <v>0.0753438725837503</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.06047611841805935</v>
+        <v>0.04752902293149833</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04234423268213443</v>
+        <v>-0.0505029484243561</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.01405960603172634</v>
+        <v>0.06289651722932341</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.006386215285583511</v>
+        <v>-0.009034705163669427</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,79 +3734,79 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1299498893161634</v>
+        <v>-0.1181677933824404</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.02367984192128774</v>
+        <v>0.1208965249444067</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.03053307396843585</v>
+        <v>0.00567103391827174</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01509516494936595</v>
+        <v>0.08599139933240182</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02057839433035879</v>
+        <v>0.07034948431626131</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01240260819385273</v>
+        <v>0.04740369200019642</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.02835337126458821</v>
+        <v>0.04544798984804881</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.04075535326468471</v>
+        <v>0.150266401716305</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.06387655567375472</v>
+        <v>-0.01833195461868346</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
@@ -3815,22 +3815,22 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.09767090188424378</v>
+        <v>-0.07789438014988352</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.07442098810963495</v>
+        <v>0.08404616891291965</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.06735353922059929</v>
+        <v>0.152425996382701</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03234934383262397</v>
+        <v>-0.001891929218014439</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.03365379991509742</v>
+        <v>-0.09245946034437709</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3871,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05017756627046171</v>
+        <v>0.1699784599978932</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,25 +3883,25 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02542976874508154</v>
+        <v>-0.0475402172245859</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02886384090269291</v>
+        <v>-0.0906033874634357</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009654646167252498</v>
+        <v>0.07171150039613816</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3910,37 +3910,37 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.006363758926963285</v>
+        <v>-0.07730478877713787</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01153540729153603</v>
+        <v>-0.01856827776982982</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.003504689528628991</v>
+        <v>-0.03183941957671436</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.007295447018941376</v>
+        <v>-0.155266277066223</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.005519464572485682</v>
+        <v>0.02183991803910662</v>
       </c>
       <c r="AH7" t="n">
         <v>-0</v>
@@ -3949,13 +3949,13 @@
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.005445047435029978</v>
+        <v>0.03647277819869631</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
@@ -3964,25 +3964,25 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02411514495648492</v>
+        <v>-0.03043768990518462</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.005117842601236839</v>
+        <v>-0.02260304348340455</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.09438292184370271</v>
+        <v>0.2293691343745251</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
@@ -3991,10 +3991,10 @@
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.01842133091288851</v>
+        <v>-0.1731146312342259</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.01938586971141706</v>
+        <v>-0.1137604611916104</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,40 +4003,40 @@
         <v>-0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02182792840807176</v>
+        <v>0.01746173861572066</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06285602895147449</v>
+        <v>-0.007110116428382946</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.05674648570784261</v>
+        <v>-0.07327278918654132</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02779407714275784</v>
+        <v>0.02429424727440051</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,25 +4045,25 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01479117354892456</v>
+        <v>0.08546280990147444</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01719261962557575</v>
+        <v>0.0437301508332287</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.02536246336359271</v>
+        <v>0.0865530883245792</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.008648143198228752</v>
+        <v>-0.01507064765732338</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.004779982034547663</v>
+        <v>-0.07171927007271395</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4084,67 +4084,67 @@
         <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.01899379467439508</v>
+        <v>-0.06982424470960685</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0037251379189915</v>
+        <v>0.006717794926154819</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.02080094470254879</v>
+        <v>0.08433482335343374</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0007320439770034675</v>
+        <v>-0.01534335109964446</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.003625385787045675</v>
+        <v>0.03553028864581901</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.005341365465180892</v>
+        <v>0.02118671776285226</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01244595856356512</v>
+        <v>-0.07322239894239357</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,145 +4153,145 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.004844351123662148</v>
+        <v>0.009515534005596888</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.02145965347844274</v>
+        <v>0.09882197234959582</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.003760907827606001</v>
+        <v>-0.03166725062926272</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02541918740356149</v>
+        <v>-0.06472060519350435</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.01116573870685757</v>
+        <v>0.04860274481609204</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0008576028537177905</v>
+        <v>-0.01649753686391873</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.009331925098680527</v>
+        <v>-0.06192075266578162</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.003915073102954768</v>
+        <v>0.01154733424809131</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.03373606331424769</v>
+        <v>-0.001686296282100892</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0159059403933847</v>
+        <v>9.96477539844259e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0199596834867576</v>
+        <v>0.05760348809280563</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0222317325769556</v>
+        <v>-0.03339637067543792</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.006858812402653142</v>
+        <v>0.008109930707286233</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02064741803410529</v>
+        <v>0.02826753644312951</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.001877178928775932</v>
+        <v>-0.02080029283160563</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01477936490065406</v>
+        <v>-0.01198205882957503</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.004208940564530229</v>
+        <v>0.09000290604286676</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
@@ -4300,31 +4300,31 @@
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.01214383169683911</v>
+        <v>-0.08007505524492177</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.009983582680915135</v>
+        <v>-0.01054446197174847</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02328899391929042</v>
+        <v>0.07587066349917115</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,25 +4333,25 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01598204253949016</v>
+        <v>0.1180156154509924</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01111642881519773</v>
+        <v>-0.03946450488004682</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.004972959251703516</v>
+        <v>0.102495904431323</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.008282117451056527</v>
+        <v>0.02308166533761733</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
@@ -4369,28 +4369,28 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.0157687597896595</v>
+        <v>-0.04660590584584966</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.01603162744069306</v>
+        <v>-0.04511060882875163</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.002502677520447931</v>
+        <v>-0.02627011097951263</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,7 +4399,7 @@
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.008103379455128104</v>
+        <v>0.08295988115756173</v>
       </c>
       <c r="GE7" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,16 +4416,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5630163587463207</v>
+        <v>0.2173584764626697</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1470498942248318</v>
+        <v>-0.07828581623734721</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1251453336046228</v>
+        <v>-0.03524882625230497</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3863470304946997</v>
+        <v>0.2305992901612075</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1124686084477243</v>
+        <v>-0.09341840245599978</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.09007254621531643</v>
+        <v>-0.0716630364261463</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4470,76 +4470,76 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1658514411033613</v>
+        <v>0.05611068381035051</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.07367816104351724</v>
+        <v>-0.0256925994676321</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05811846074204711</v>
+        <v>-0.06855668598476043</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.06221845402829147</v>
+        <v>-0.02700292524879115</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001246685860595559</v>
+        <v>-0.1075244369561857</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.06304257019689287</v>
+        <v>-0.02191658209600227</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0969113182066584</v>
+        <v>0.08076382011338724</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.07377838152320645</v>
+        <v>-0.06034776782255048</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.05743047437628553</v>
+        <v>0.06310069317297935</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4548,55 +4548,55 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.6816541240984746</v>
+        <v>0.237039510470387</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01783777209693958</v>
+        <v>-0.0545862931811455</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.05248365871414144</v>
+        <v>-0.1630534483810313</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.09903171857177416</v>
+        <v>0.01617325335361144</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1859029500637389</v>
+        <v>-0.05178086050438959</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.2366117426154909</v>
+        <v>0.001469912814561083</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -4605,16 +4605,16 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1190237212524956</v>
+        <v>-0.009903907326447817</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.1457049271979755</v>
+        <v>0.04007836602328077</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1228866433430206</v>
+        <v>0.09303941984300954</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4626,31 +4626,31 @@
         <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2058743048774865</v>
+        <v>0.0874409203593309</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.02555764591885937</v>
+        <v>-0.04389831921167162</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.007091994802788783</v>
+        <v>-0.02344876052352524</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -4659,22 +4659,22 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1738023192900881</v>
+        <v>-0.1039400572010369</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.006640504189996144</v>
+        <v>0.08181600659419155</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01818576483866869</v>
+        <v>0.01159989099433763</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,43 +4686,43 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01871106651271206</v>
+        <v>-0.02433830442380548</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.07020647852426405</v>
+        <v>0.05837721590511996</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.08066941885444386</v>
+        <v>0.004741824860149453</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.1400432581827839</v>
+        <v>-0.107430850359048</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.07084932339236036</v>
+        <v>0.0906252554389243</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.04102693157053303</v>
+        <v>0.02440280319524286</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
@@ -4734,22 +4734,22 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.05132936474330026</v>
+        <v>-0.06392570022896979</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1187949018368941</v>
+        <v>0.002683442561312673</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03539012008476434</v>
+        <v>-0.0351808203097721</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
@@ -4761,25 +4761,25 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.1338804048637321</v>
+        <v>-0.06272845202901639</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.03484174306465382</v>
+        <v>-0.04942457994462075</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.1001495725297134</v>
+        <v>-0.06054837558935407</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4794,16 +4794,16 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.08515119579093161</v>
+        <v>-0.01325182983916521</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.02087044544038885</v>
+        <v>0.05547641689147549</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.0003434812765714191</v>
+        <v>-0.0008558270452945</v>
       </c>
       <c r="EB8" t="n">
         <v>-0</v>
@@ -4815,160 +4815,160 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.1304360608735296</v>
+        <v>-0.07606345804274643</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.001916890882999341</v>
+        <v>0.06398452473688304</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0722954766902582</v>
+        <v>0.04632518909246774</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.02381524590599598</v>
+        <v>-0.04457977965161265</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.01802976955186862</v>
+        <v>0.02544807680489445</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01470823754320003</v>
+        <v>0.02044842447923504</v>
       </c>
       <c r="ET8" t="n">
         <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1325480812699146</v>
+        <v>-0.1114313241413328</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.02634693256735648</v>
+        <v>0.1068507847105537</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.02336874266619159</v>
+        <v>-1.492375536942623e-05</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.006002253151007166</v>
+        <v>0.09350836754538285</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.024961791619951</v>
+        <v>0.06088857022450656</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02576087890935747</v>
+        <v>0.000687888826457122</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.02813353548993136</v>
+        <v>0.02783421447540756</v>
       </c>
       <c r="FR8" t="n">
         <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.06033835977392239</v>
+        <v>0.1538701142559844</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.0953484101718403</v>
+        <v>-0.03478470915076781</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.09806507263838728</v>
+        <v>-0.05915438743771619</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.05945735538107197</v>
+        <v>0.03132629490872423</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,15 +4977,15 @@
         <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1084636909099465</v>
+        <v>0.2322346922661858</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,13 +4994,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03508689626208651</v>
+        <v>0.05135993026557407</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08386992567202251</v>
+        <v>-0.234651958242811</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5009,10 +5009,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07456234332974164</v>
+        <v>0.2860953529376191</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01319960489974576</v>
+        <v>-0.04911948124784331</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06799702865425424</v>
+        <v>-0.220763742063671</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01935860097122919</v>
+        <v>0.05086565578552366</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,40 +5048,40 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02356555995406321</v>
+        <v>-0.104297685172658</v>
       </c>
       <c r="X9" t="n">
-        <v>0.000729878765296383</v>
+        <v>-0.1126478187342622</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.001190442627780579</v>
+        <v>-0.09004059972807503</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.00569765434252216</v>
+        <v>-0.1495897487894384</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.006001866073399612</v>
+        <v>0.02586461263395353</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5093,88 +5093,88 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0291315649052692</v>
+        <v>0.102651597282161</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.009998166467945645</v>
+        <v>-0.01409515725629619</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.02354075430949724</v>
+        <v>-0.1133165710931718</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1176142145806648</v>
+        <v>0.5297330125852169</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.05623130114361507</v>
+        <v>-0.1921181162941892</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.08599787083772228</v>
+        <v>-0.2161632894382817</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03888908583173647</v>
+        <v>-0.1133986229728433</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.03266563442270084</v>
+        <v>0.04008641084712903</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.04974430266937271</v>
+        <v>-0.1063008194089055</v>
       </c>
       <c r="BI9" t="n">
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03357005222885633</v>
+        <v>0.1018354748783759</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,25 +5183,25 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.009770485387403997</v>
+        <v>0.03873838081237337</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0008333069464059094</v>
+        <v>0.1226949848401529</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.02610727331435032</v>
+        <v>0.1674564982088524</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,91 +5210,91 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.0282407661084298</v>
+        <v>-0.03527380216974951</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.02634175495481197</v>
+        <v>-0.1563927625223003</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.02557833570535583</v>
+        <v>-0.1249019684307568</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001555485108946643</v>
+        <v>0.01542933889640586</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0395584293642655</v>
+        <v>0.1213535850149616</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.006116548373875794</v>
+        <v>-0.08681669354247515</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01188027288204094</v>
+        <v>0.08856153202321208</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.006735998859132856</v>
+        <v>-0.00239293339340611</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.02127951252301643</v>
+        <v>-0.119229695052989</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-4.653921272417935e-05</v>
+        <v>0.01431555172533871</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.04390612897799995</v>
+        <v>0.1406278737392966</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -5303,25 +5303,25 @@
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.005117207034683711</v>
+        <v>-0.1188210378145639</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05297403071774665</v>
+        <v>-0.06103762150096529</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.002807276706293893</v>
+        <v>0.02446853618731921</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -5330,13 +5330,13 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.001245884959459419</v>
+        <v>-0.114056982351331</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01969436668937592</v>
+        <v>0.03355446563149177</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.001927151626423281</v>
+        <v>0.2006202647456038</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02947764215360672</v>
+        <v>0.0004944066395645098</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01388444322364039</v>
+        <v>0.06550192504754421</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.04029710712411848</v>
+        <v>0.05915970581309608</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,49 +5390,49 @@
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02695677256837228</v>
+        <v>-0.08813061766319608</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>6.486901780084709e-05</v>
+        <v>-0.03274772292328765</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.04207942256367199</v>
+        <v>0.02948958389381575</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.01456102416744852</v>
+        <v>-0.02921544402648885</v>
       </c>
       <c r="EQ9" t="n">
         <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01438599852725218</v>
+        <v>-0.0946807368935183</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0003007163443406968</v>
+        <v>-0.02092062907775352</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,106 +5444,106 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.01918017194660409</v>
+        <v>-0.1352844489088482</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.004753746759323633</v>
+        <v>-0.009635118915430955</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.04010669280880503</v>
+        <v>0.1310505972722731</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01304170147846889</v>
+        <v>0.1210150079136416</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.003696217818561277</v>
+        <v>-0.02088983190220356</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.02954786790343739</v>
+        <v>0.08437511121729313</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.007900631044082024</v>
+        <v>0.09783534312391835</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.03543406425753316</v>
+        <v>-0.0175541759317788</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04713274127065178</v>
+        <v>0.02278631129112623</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.008715145081860902</v>
+        <v>-0.01023697544682227</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.004093186456028223</v>
+        <v>0.1692547256634893</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0960286363108287</v>
+        <v>0.2731092898662322</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,25 +5563,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03652720490224504</v>
+        <v>-0.00852020114051984</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07575714596018408</v>
+        <v>-0.215961133993485</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08386760904339001</v>
+        <v>0.3313413915461835</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,25 +5590,25 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02591410292433933</v>
+        <v>-0.1113154322616817</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04812385366084201</v>
+        <v>-0.1698355047703132</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01009339710324868</v>
+        <v>0.1132986239591662</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -5617,37 +5617,37 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.004223443773440477</v>
+        <v>-0.1396860138055208</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01425654537955637</v>
+        <v>-0.03891418303516855</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.008661368072125161</v>
+        <v>-0.05317021099066692</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0002516408855123936</v>
+        <v>-0.2475826802270693</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.007119253467375921</v>
+        <v>0.05468145126767211</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01127965407729632</v>
+        <v>0.04941732189726002</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
@@ -5671,25 +5671,25 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02202891924970486</v>
+        <v>-0.05442734277925319</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.001525075263417325</v>
+        <v>-0.004284221774778907</v>
       </c>
       <c r="AQ10" t="n">
         <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1067473287331068</v>
+        <v>0.3941451668452549</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.03193675247746069</v>
+        <v>-0.2559762437599341</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.04983186736905913</v>
+        <v>-0.227981927226069</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
@@ -5716,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03199738614729786</v>
+        <v>-0.007338530471009653</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.04912184257728795</v>
+        <v>0.01892731100221588</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.06505599318008679</v>
+        <v>-0.1039265446891456</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03361529702503533</v>
+        <v>0.04745685208514786</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,13 +5752,13 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02264228203403736</v>
+        <v>0.10718741685618</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01583012897545901</v>
+        <v>0.04596854731849693</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,10 +5767,10 @@
         <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.02972335585338289</v>
+        <v>0.1354664362469093</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.007618609080487277</v>
+        <v>-0.03931875719319128</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.007715657614221844</v>
+        <v>-0.05771256103538863</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,133 +5791,133 @@
         <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02060453109701021</v>
+        <v>-0.1071773165934876</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.002750934400927452</v>
+        <v>0.0146768336739776</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02905047561481533</v>
+        <v>0.1063936308912532</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.001402342926165452</v>
+        <v>-0.04704649588944083</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.006674437331533583</v>
+        <v>0.07850665179023196</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.001260337717403466</v>
+        <v>0.07560469240783504</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.01425498450996875</v>
+        <v>-0.1090469722361679</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.005356189355216204</v>
+        <v>0.01684576627178744</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02991708579328651</v>
+        <v>0.134739273424531</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.009771544469172446</v>
+        <v>-0.08644688664095543</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03290452072171841</v>
+        <v>-0.1509491307825284</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.0003058929837241106</v>
+        <v>0.04728636560910433</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.002556045158417577</v>
+        <v>-0.006428096909546424</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.005398683597790988</v>
+        <v>-0.08220284398563162</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.0196050489993177</v>
+        <v>0.04598787734149998</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5926,13 +5926,13 @@
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.03666723694145066</v>
+        <v>-0.01546685933139843</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02264239740117099</v>
+        <v>-0.01196290521541887</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.01680323512957665</v>
+        <v>0.09813108190412084</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
@@ -5956,49 +5956,49 @@
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02238967053418871</v>
+        <v>-0.05603023348561711</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.003660928541685583</v>
+        <v>0.00200916645077721</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.03127239286501875</v>
+        <v>0.03320940240914265</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.002507501387223675</v>
+        <v>-0.03447453805235223</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02510890883368625</v>
+        <v>0.01051950256024899</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.006746841060494302</v>
+        <v>0.1358101097230702</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6007,58 +6007,58 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.01249982837142776</v>
+        <v>-0.1212901207164859</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01029853314482952</v>
+        <v>-0.009598307423607825</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.03099885648355556</v>
+        <v>0.09681231374881256</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02094637909310562</v>
+        <v>0.1758484981768267</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01494669753366782</v>
+        <v>-0.04305631819975862</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.006758628671178858</v>
+        <v>0.1491500984532559</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.009306549673940191</v>
+        <v>0.04758465837725766</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
@@ -6076,28 +6076,28 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.01969353670904423</v>
+        <v>-0.06513207909759536</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.01191784116217887</v>
+        <v>-0.08003203563612801</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.002602234558131938</v>
+        <v>-0.03040334081288252</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,7 +6106,7 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.003908739077853748</v>
+        <v>0.135055284363379</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4091146085926858</v>
+        <v>0.2920261529853228</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.09587746788475285</v>
+        <v>-0.1273232190313716</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.05363043912734773</v>
+        <v>-0.02249315065690234</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,16 +6150,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2943027783757008</v>
+        <v>0.3030140012893212</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.07201377730101863</v>
+        <v>-0.1202547793894841</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.05275463120334871</v>
+        <v>-0.06491962397713361</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6174,28 +6174,28 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1126869706635998</v>
+        <v>0.06295905547047154</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003602224365627727</v>
+        <v>-0.02213996694490702</v>
       </c>
       <c r="W11" t="n">
-        <v>0.06839946981490258</v>
+        <v>-0.06827957325650037</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,43 +6204,43 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1411738122165255</v>
+        <v>-0.07248653282610511</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01963020288842808</v>
+        <v>-0.1085519170337063</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.08596317604364226</v>
+        <v>-0.1036564185372747</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0383509873428518</v>
+        <v>0.1175139230489904</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.09420297093003979</v>
+        <v>-0.09688277643500123</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0543450213567745</v>
+        <v>0.02484489209281216</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4443227812606321</v>
+        <v>0.3353463206826821</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.02615109359777553</v>
+        <v>-0.1754874447782689</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1400250172296933</v>
+        <v>-0.2398717904819142</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6276,25 +6276,25 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02640490067339411</v>
+        <v>-0.03497205068334186</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.04146243950768309</v>
+        <v>-0.04169793125927534</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2191886051078534</v>
+        <v>0.01743102991187168</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,85 +6303,85 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01755304775908243</v>
+        <v>0.01183240130978882</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.1120308795180182</v>
+        <v>0.05463689547418763</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1237501614651777</v>
+        <v>0.01960278329238925</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1397553417808557</v>
+        <v>0.1528307236497994</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.005624406532427283</v>
+        <v>-0.05768010527067011</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.03578073449688661</v>
+        <v>-0.03084126774034402</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1086416979389735</v>
+        <v>-0.1174917950774833</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.01610407617971211</v>
+        <v>0.131488894218673</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01139866433603148</v>
+        <v>-0.005434354244206258</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6390,52 +6390,52 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.005357932289850771</v>
+        <v>-0.06746229776826708</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.07642898378277184</v>
+        <v>0.1246540245076733</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.06318274108489899</v>
+        <v>0.03828020007657705</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.09664462730545512</v>
+        <v>-0.113998602290396</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04192639392799768</v>
+        <v>0.1433915964098089</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.008904618971935228</v>
+        <v>0.01240547037567005</v>
       </c>
       <c r="DA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,22 +6447,22 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.004102065007883418</v>
+        <v>-0.1118397577566651</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.00526006539640128</v>
+        <v>-0.01160083451021952</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02718198243534795</v>
+        <v>-0.05967227782272375</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
@@ -6471,25 +6471,25 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0825895417785841</v>
+        <v>-0.05575546785299297</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.1065888284771941</v>
+        <v>0.05905819306862316</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.07037031958009045</v>
+        <v>-0.02899816304541485</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
@@ -6498,19 +6498,19 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.01219561271302896</v>
+        <v>0.002186369183785625</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.02097166125542065</v>
+        <v>0.0744085569866704</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.004997457316349168</v>
+        <v>-0.02712936934591518</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
@@ -6528,22 +6528,22 @@
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.06975982333032571</v>
+        <v>-0.07367560300944896</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.04396017234337046</v>
+        <v>0.1058231657426686</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.09468805273973693</v>
+        <v>0.02273754631417022</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,25 +6552,25 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1003725487013677</v>
+        <v>-0.07724758639111105</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0.08278114822246482</v>
+        <v>-0.08062435257359718</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.02104124228799349</v>
+        <v>-0.00413490950193103</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,25 +6579,25 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.0964370636840438</v>
+        <v>-0.129437361881055</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.03199127202671286</v>
+        <v>0.1590604158260745</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.01598719692102281</v>
+        <v>-0.008320615537414599</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
@@ -6606,52 +6606,52 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.0154710102899776</v>
+        <v>0.1128895698516709</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.07707684330315785</v>
+        <v>0.0871957198593598</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.00312070537540071</v>
+        <v>-0.00695582684500207</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.003710621187487076</v>
+        <v>0.03761040193213614</v>
       </c>
       <c r="FR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.1136518650394632</v>
+        <v>0.1777166300746238</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.03115538699795922</v>
+        <v>-0.0266103170398595</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
@@ -6660,39 +6660,39 @@
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.009287869999601829</v>
+        <v>-0.07062607075627031</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.05360708779051649</v>
+        <v>0.06869382140881627</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2398411063717481</v>
+        <v>0.3818336392512437</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,10 +6701,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05527482646009003</v>
+        <v>0.06735476143572681</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1752120159310961</v>
+        <v>-0.3991984993520522</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2063706163139049</v>
+        <v>0.4260714637978042</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,64 +6728,64 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.007682749902248502</v>
+        <v>-0.1137354820268274</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1145834526286417</v>
+        <v>-0.3587279789386869</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02572195047978222</v>
+        <v>0.1310222196745848</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.04028655493787296</v>
+        <v>-0.06641511504806757</v>
       </c>
       <c r="X12" t="n">
-        <v>0.002291569317161726</v>
+        <v>-0.08646255750784691</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.005786000536427084</v>
+        <v>-0.109807664858781</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001879626760786922</v>
+        <v>-0.229465078362826</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.02349798191637865</v>
+        <v>0.1034204492728152</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03083912626118425</v>
+        <v>0.1254772049664125</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.01724383555866729</v>
+        <v>-0.02331733116145402</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.06168936543441657</v>
+        <v>-0.1020946524355028</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,37 +6824,37 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1943706496431351</v>
+        <v>0.5777287919769352</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.04657380056006627</v>
+        <v>-0.3071472355985048</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.1371479801216305</v>
+        <v>-0.4131604923791957</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.07076363010247673</v>
+        <v>-0.08426798305299675</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.05659753675603613</v>
+        <v>0.05179590131316942</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.07413022569319608</v>
+        <v>-0.08093545645808103</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
         <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0522113352444403</v>
+        <v>0.09876042442942506</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02856320853839138</v>
+        <v>0.06038769380340057</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0122828875254019</v>
+        <v>0.0978055795018142</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.06783323715480429</v>
+        <v>0.1959107348114841</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,37 +6917,37 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.0175638811197921</v>
+        <v>-0.02774476101725484</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.02419130925777675</v>
+        <v>-0.1241011799578689</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05269872106903455</v>
+        <v>-0.1598942378569255</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.001965456515029512</v>
+        <v>0.03511606174266348</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.05210537067610756</v>
+        <v>0.134480641590343</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6962,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.004588242935832325</v>
+        <v>-0.1276958936969936</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
@@ -6971,37 +6971,37 @@
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.003137616777878778</v>
+        <v>0.1780032897146153</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.03707630019124201</v>
+        <v>-0.02671475234574399</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04858251681226407</v>
+        <v>-0.1601053756898077</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.00474468829214552</v>
+        <v>0.02584174980349675</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.05641450491970772</v>
+        <v>0.1702658188821433</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
@@ -7010,40 +7010,40 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.005913120870117308</v>
+        <v>0.02784534664309366</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07110915933712124</v>
+        <v>-0.06935605455197125</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.002859681625727157</v>
+        <v>0.04973727137631134</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.02202449271683344</v>
+        <v>-0.1475259592285085</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
@@ -7052,16 +7052,16 @@
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01408393324576709</v>
+        <v>0.003223188303620595</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.01115438146903689</v>
+        <v>0.1551864128497741</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,46 +7070,46 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.05074967448610333</v>
+        <v>-0.02834390409484493</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.02764434665611608</v>
+        <v>0.08511999129577245</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.02486357109222454</v>
+        <v>0.08458491891629372</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04853380045888847</v>
+        <v>-0.05543079565188232</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01634481265790279</v>
+        <v>-0.0406728149261867</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0607703514886459</v>
+        <v>0.03138273564726495</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
@@ -7118,13 +7118,13 @@
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03622891805301952</v>
+        <v>-0.06896805478722434</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
@@ -7133,13 +7133,13 @@
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01210412007164178</v>
+        <v>-0.1122591855722063</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.0115085465403298</v>
+        <v>0.009320212506216284</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,7 +7151,7 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0462223295466317</v>
+        <v>-0.1757881771270006</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,52 +7160,52 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.005214681248333999</v>
+        <v>0.008817526612889495</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.05140489862733341</v>
+        <v>0.1502790282862537</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.01300282475641729</v>
+        <v>0.1443889851946855</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.00561449708555917</v>
+        <v>-0.06170223035782122</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.03020343768845524</v>
+        <v>0.1814815521180231</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.004679832130202722</v>
+        <v>0.04763083323568426</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,37 +7214,37 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.02481829795151622</v>
+        <v>-0.06896517890828216</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.03216556044697974</v>
+        <v>-0.02400024449546361</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.00880790406967029</v>
+        <v>-0.03736386977621955</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.007705279337345615</v>
+        <v>0.2228666447718054</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,46 +7261,46 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3379094323175996</v>
+        <v>0.2293227462591774</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1018066738267382</v>
+        <v>-0.09676135119564157</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.09935426822137017</v>
+        <v>0.02888575216324062</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.051680062753987</v>
+        <v>-0.06973234444907991</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2725808666746972</v>
+        <v>0.2472959509131368</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.06146486414439051</v>
+        <v>-0.1101830839248955</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05109274015021552</v>
+        <v>-0.03013456263381068</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.05245049879505293</v>
+        <v>-0.05287382220981986</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7309,25 +7309,25 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06992600404405942</v>
+        <v>0.0812176053531838</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.02051093893029326</v>
+        <v>-0.04365827624109184</v>
       </c>
       <c r="W13" t="n">
-        <v>0.08398804465128336</v>
+        <v>-0.07874410479666959</v>
       </c>
       <c r="X13" t="n">
-        <v>0.007649422257226272</v>
+        <v>-0.05729729096350579</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
@@ -7339,130 +7339,130 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05437623555885013</v>
+        <v>-0.08125264032614277</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01960746061877402</v>
+        <v>-0.09447849502655692</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.02118903792178714</v>
+        <v>-0.06089358898901855</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.01668982390457304</v>
+        <v>0.05137808358458914</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.009491794921335327</v>
+        <v>0.04808914961437392</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.05913271753550518</v>
+        <v>-0.05772253291709541</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.05933833295789907</v>
+        <v>0.05416815689777353</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.03729005916439004</v>
+        <v>-0.03912627406787313</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3110167039591227</v>
+        <v>0.2580634742319057</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.03770388101133364</v>
+        <v>-0.05356182360020059</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.03074244852352222</v>
+        <v>-0.06894944830366966</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.04815230333947722</v>
+        <v>-0.09428419521400398</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04948406287749423</v>
+        <v>-0.01872940107873146</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.07100459942513031</v>
+        <v>-0.08330452894423394</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1101952054383101</v>
+        <v>-0.0476461660211097</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.0792444091329805</v>
+        <v>-0.03800941893585112</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07490069907877341</v>
+        <v>-0.03042788671771216</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.05755711073683852</v>
+        <v>0.05890557771192222</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1179974277944906</v>
+        <v>0.02798516594026612</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.03021947906267175</v>
+        <v>-0.001209801233012391</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
@@ -7471,31 +7471,31 @@
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.08158434960576105</v>
+        <v>0.1010396283907165</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.004717049072413738</v>
+        <v>-0.02525447667214989</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.01242961291228278</v>
+        <v>0.0142364951774811</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.007284627895597779</v>
+        <v>-0.04848839613441667</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,19 +7504,19 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.07632327409785855</v>
+        <v>-0.07685341144418227</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.002136137800677467</v>
+        <v>0.06937349582299734</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0002689941560019523</v>
+        <v>-0.01386456109043325</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02781241478733188</v>
+        <v>0.02438058593237826</v>
       </c>
       <c r="CJ13" t="n">
         <v>0</v>
@@ -7531,52 +7531,52 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.004430542822254702</v>
+        <v>-0.02189207576844652</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.0559185184928236</v>
+        <v>0.1138898025430263</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.0752344133718129</v>
+        <v>0.03314033395617234</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.04529481847192484</v>
+        <v>0.03489725036342935</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.05870216976706583</v>
+        <v>-0.07768401109872339</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.02855619806891431</v>
+        <v>0.07248821942306309</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.003903052864654216</v>
+        <v>-0.002477599970079088</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0293410972011185</v>
+        <v>0.03253080867377942</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>-0</v>
@@ -7585,19 +7585,19 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.0150245984696761</v>
+        <v>-0.03575418393409782</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.04981702742530751</v>
+        <v>-0.0006283499418585578</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.005430269659957575</v>
+        <v>0.01223538382552863</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01974980072932718</v>
+        <v>0.02377302559377491</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
@@ -7606,25 +7606,25 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.01332874685762348</v>
+        <v>-0.009128918125255637</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.06176468319871725</v>
+        <v>0.0119116790769085</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.02503571402290597</v>
+        <v>-0.06563499251438121</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.02537586036662908</v>
+        <v>0.01725991126341363</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7639,73 +7639,73 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.04524791063124025</v>
+        <v>-0.004629240962313726</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.02489559646529383</v>
+        <v>0.06440535163663656</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.03054309196446194</v>
+        <v>-0.009387492384609888</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0517086703804061</v>
+        <v>0.00169270565471824</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.08725051217310446</v>
+        <v>-0.06668886941313049</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.03778758013969472</v>
+        <v>0.06183742535298908</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.06812579185327362</v>
+        <v>0.03149515230431024</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01931817051451819</v>
+        <v>-0.03100768788290859</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03998279848822533</v>
+        <v>-0.02518067623466508</v>
       </c>
       <c r="EQ13" t="n">
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.004356767208551909</v>
+        <v>0.04459343062973309</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02666339699550235</v>
+        <v>-0.01319680670031427</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.02918241725320382</v>
+        <v>0.047512969526105</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7720,19 +7720,19 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05952409432047424</v>
+        <v>-0.07979536998016053</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.002112486475449254</v>
+        <v>0.09262681317023605</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.01496714966355858</v>
+        <v>-0.02903731213371775</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03371557661787723</v>
+        <v>0.02920422871010689</v>
       </c>
       <c r="FD13" t="n">
         <v>0</v>
@@ -7747,22 +7747,22 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.0289528375208692</v>
+        <v>0.1001904467200465</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.05508469682261196</v>
+        <v>0.05746675828859554</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01186807337628144</v>
+        <v>0.01482763905377418</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.007130740801651334</v>
+        <v>0.07816391973510835</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
@@ -7771,58 +7771,58 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.003907729427633204</v>
+        <v>0.007177939423570134</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01411860714299012</v>
+        <v>0.1075157492171658</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03556256880421125</v>
+        <v>-0.01350476302129188</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.04097767206796805</v>
+        <v>-0.04272726092194789</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.03982656841238666</v>
+        <v>-0.07184177090250612</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.07647594802186219</v>
+        <v>0.03800156092332981</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.04232593444881398</v>
+        <v>0.04157176270901347</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
         <v>0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,49 +7830,49 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3126690855549613</v>
+        <v>0.2226651036714107</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05609969321217406</v>
+        <v>-0.09785737252886609</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02932833606765736</v>
+        <v>-0.01767154126188185</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2101123737070544</v>
+        <v>0.2641374729202806</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07797705961177792</v>
+        <v>-0.1152163826256513</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.03968803206015536</v>
+        <v>-0.04528668758874435</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -7884,70 +7884,70 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07947666403058534</v>
+        <v>0.03815084528867083</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.04850897464439739</v>
+        <v>-0.03017582064574498</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1267073574977695</v>
+        <v>-0.03688978544675384</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.09900532713295686</v>
+        <v>-0.04760722288300123</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0004380603901613554</v>
+        <v>-0.08506823448317444</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.05332464803519147</v>
+        <v>-0.05468300113138808</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.04513340908333478</v>
+        <v>0.06719867156678599</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.05291092091908257</v>
+        <v>-0.06777675925761627</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.02192472366335089</v>
+        <v>0.04630438284209094</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7956,61 +7956,61 @@
         <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3058439508309148</v>
+        <v>0.2076141451633955</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1337846595925798</v>
+        <v>-0.06127478377390019</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1506976920306103</v>
+        <v>-0.09971112077615703</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02051277376071558</v>
+        <v>-0.002530390654185088</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1561109404897617</v>
+        <v>-0.03156997255448277</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1154279559640934</v>
+        <v>-0.01870182283020826</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,19 +8019,19 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.07265545614849796</v>
+        <v>-0.01045621215085403</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.0072706578558068</v>
+        <v>0.02799366481008475</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.188614409087571</v>
+        <v>0.04673805549184153</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8040,52 +8040,52 @@
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.08642450399784528</v>
+        <v>0.08562761821386494</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.03556358969688526</v>
+        <v>-0.02711753217494993</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.06419239952032475</v>
+        <v>-0.004577417823970337</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.07938469090644715</v>
+        <v>-0.07486579213736336</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.02080134538854761</v>
+        <v>0.06171728105326138</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.005908944081764145</v>
+        <v>-0.0004718696405128329</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
         <v>0</v>
@@ -8094,28 +8094,28 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.02010011691712798</v>
+        <v>-0.05870878034810847</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1174806778982358</v>
+        <v>0.1214181180467296</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.09495523483118722</v>
+        <v>0.01960398476623997</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
@@ -8124,46 +8124,46 @@
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.05420749147733353</v>
+        <v>-0.0723751052792523</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.0008864630612549593</v>
+        <v>0.0658668609902926</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01253457510804198</v>
+        <v>0.005815228936733757</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.03846277814740031</v>
+        <v>-0.03998386926371473</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.02967720598733065</v>
+        <v>0.03232703596090521</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.02226172217234561</v>
+        <v>-0.03497524659670377</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
@@ -8181,19 +8181,19 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04723708888648961</v>
+        <v>-0.03506274228047825</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.04886210886493794</v>
+        <v>-0.01530411774808813</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.04156517930939408</v>
+        <v>-0.01952346518066899</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
@@ -8202,76 +8202,76 @@
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.02856646454190513</v>
+        <v>-0.006848649195886498</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.03167951797952559</v>
+        <v>0.06310867991718347</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.007688091270068147</v>
+        <v>-0.02519074484430198</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.0729841445881694</v>
+        <v>-0.05507515637767944</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.009345240150265142</v>
+        <v>0.03895209726477578</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.08621811376700454</v>
+        <v>0.03974535911906883</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.02299091103680739</v>
+        <v>-0.02576261593631088</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02036313880973147</v>
+        <v>0.03396901745829105</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02591097598833067</v>
+        <v>-0.01712867677106123</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8283,49 +8283,49 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.05534275525002808</v>
+        <v>-0.08050284811066057</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.03168771516735476</v>
+        <v>0.07891491022703302</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.007171445547234447</v>
+        <v>-0.008786372113047976</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.008561735286078833</v>
+        <v>0.0807933623706627</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001329848477741539</v>
+        <v>0.04703120382577917</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.03200777456784959</v>
+        <v>-0.008301851799541364</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8337,25 +8337,25 @@
         <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.002058810627453542</v>
+        <v>0.001971123905602779</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.02028086715056568</v>
+        <v>0.07160383786884457</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.004479644379169727</v>
+        <v>-0.009361296926734196</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
@@ -8367,39 +8367,39 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.01269615824321753</v>
+        <v>-0.05198097099517154</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.1149840544964474</v>
+        <v>0.01836639099926198</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.193964810082618</v>
+        <v>-0.4767163978337327</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
@@ -8408,13 +8408,13 @@
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1922260458404778</v>
+        <v>0.1470664015923909</v>
       </c>
       <c r="F15" t="n">
-        <v>1.211530977098627</v>
+        <v>0.6733912361640824</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8423,10 +8423,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.070211935124776</v>
+        <v>-0.6224449757320512</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
@@ -8435,13 +8435,13 @@
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02201537352693178</v>
+        <v>0.2448336656899933</v>
       </c>
       <c r="O15" t="n">
-        <v>0.938398987481615</v>
+        <v>0.8527584076570665</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,79 +8450,79 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0951525918059429</v>
+        <v>-0.1761908761431215</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3669606335354595</v>
+        <v>0.1409587743592437</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1828576629238651</v>
+        <v>0.1334215335122954</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.0304206682131196</v>
+        <v>-0.06470287596692648</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1024325580096185</v>
+        <v>0.3802066842356869</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1063272937071937</v>
+        <v>-0.03789459522781631</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
         <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.1391143018511057</v>
+        <v>-0.1466543928102609</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.05621921865319129</v>
+        <v>-0.01018596254360176</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.2952230277035196</v>
+        <v>0.1440901502485856</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -8531,37 +8531,37 @@
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.6383394544120172</v>
+        <v>-0.801962344972294</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
         <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.3490067555960655</v>
+        <v>0.1660149119304125</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.9324293460478125</v>
+        <v>0.6426871109294162</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.3181031859854707</v>
+        <v>0.2401471322293366</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
@@ -8570,43 +8570,43 @@
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1515665436303896</v>
+        <v>0.1308517042236957</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.2793450839909461</v>
+        <v>-0.07728253044402474</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
         <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.2557876027705215</v>
+        <v>-0.2883670596082784</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.1308909087668397</v>
+        <v>-0.2100041044992967</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.08581863941846882</v>
+        <v>-0.04739304463454729</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
@@ -8615,19 +8615,19 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.6009569533865546</v>
+        <v>-0.529675681956574</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.09345967082862536</v>
+        <v>0.007343670709310258</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.3027189493763652</v>
+        <v>0.2922501008003208</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8636,40 +8636,40 @@
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.2438828411840325</v>
+        <v>0.1660462119992663</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
         <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.0552773167279562</v>
+        <v>-0.07641919724219984</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0.247309653224121</v>
+        <v>-0.2003970667928384</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.04435216166219987</v>
+        <v>0.3105926137769304</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2425794425663044</v>
+        <v>-0.05628325199644229</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0175520827755185</v>
+        <v>-0.06892836807791675</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
         <v>0</v>
@@ -8696,100 +8696,100 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.2258866905442552</v>
+        <v>0.1497095524273809</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY15" t="n">
         <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.04792423933088005</v>
+        <v>-0.09029610767069543</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0.2579978936794413</v>
+        <v>-0.2396890834555112</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.3179367113580585</v>
+        <v>0.1311428656294512</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.1468500278815038</v>
+        <v>0.06905609673524184</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.2161335342303346</v>
+        <v>-0.1235467976643764</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.06499021968471186</v>
+        <v>-0.01416840471735861</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.03573354998926257</v>
+        <v>0.09973956710554964</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.2377146263889717</v>
+        <v>-0.1335385297937485</v>
       </c>
       <c r="DT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.2345187630396724</v>
+        <v>0.1342171154039321</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.1549554009035874</v>
+        <v>0.0358093326919687</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.06153521427955334</v>
+        <v>-0.02859837379648246</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8798,67 +8798,67 @@
         <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.1737655362824672</v>
+        <v>0.02627908880742359</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.1478676183426679</v>
+        <v>-0.05883070567801679</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0.0639609158397583</v>
+        <v>-0.02269934211699293</v>
       </c>
       <c r="EL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.1822345896356057</v>
+        <v>0.1058807997995939</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.02661642006401604</v>
+        <v>-0.0363566615981197</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.05683657440870035</v>
+        <v>0.1670141042414256</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.2184508818054637</v>
+        <v>0.2006593522495504</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
@@ -8867,13 +8867,13 @@
         <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.0650833534894894</v>
+        <v>-0.03163346288127574</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0.2266763220843139</v>
+        <v>-0.2141519278431185</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
@@ -8885,7 +8885,7 @@
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.01278773294334091</v>
+        <v>-0.145042565627782</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,64 +8894,64 @@
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.08199915514518627</v>
+        <v>0.1274250259707039</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0.14480519820992</v>
+        <v>-0.2563691766906415</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01126291223235046</v>
+        <v>-0.01621382102223707</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01067520204748289</v>
+        <v>0.01344988634934693</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0.09610352289349863</v>
+        <v>0.1429345581088729</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.01631459612626653</v>
+        <v>0.03439332969544784</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.06332839467321839</v>
+        <v>-0.1094515020655147</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8775227468829905</v>
+        <v>0.8201982303265568</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04117618506661069</v>
+        <v>-0.2856028852484281</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.089378577225035</v>
+        <v>-0.7517421016009412</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7581596308278425</v>
+        <v>1.027750979643394</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,13 +9004,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03747571768386505</v>
+        <v>-0.8896327481670662</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8772230941818847</v>
+        <v>-0.875566126461332</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0</v>
@@ -9019,10 +9019,10 @@
         <v>-0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07355096350201476</v>
+        <v>0.2479646099607913</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,43 +9031,43 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.07622096914973003</v>
+        <v>-0.181020687120302</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1519630272581766</v>
+        <v>-0.1193934150137416</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1724196652705695</v>
+        <v>0.211525061415752</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.05531048439436353</v>
+        <v>-0.3900590054079175</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0809596880409853</v>
+        <v>-0.1809360355722753</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.07531932940220312</v>
+        <v>0.316670480692462</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.1067823732600553</v>
+        <v>0.1087086466012727</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.2128183910205817</v>
+        <v>-0.1514384289502892</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,22 +9100,22 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5548147448219746</v>
+        <v>1.601652994434226</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.01446490922922903</v>
+        <v>-0.2447517938968448</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.7404926585487465</v>
+        <v>-0.5386363971908255</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -9124,13 +9124,13 @@
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.2410164237641497</v>
+        <v>-0.5550311856360464</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,10 +9139,10 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1587069560354654</v>
+        <v>-0.2414507124034931</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.2176224116424044</v>
+        <v>-0.001440162408664457</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
@@ -9154,10 +9154,10 @@
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.2197765468695922</v>
+        <v>0.1333962426938703</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
@@ -9166,40 +9166,40 @@
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.01489101528714665</v>
+        <v>0.1693328073649228</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0.08930058521743735</v>
+        <v>0.1232964432530582</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
         <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.282026920426048</v>
+        <v>0.6116697923534484</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01845042379260716</v>
+        <v>-0.2170438029351986</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.372552497492137</v>
+        <v>-0.3002565138420575</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
         <v>-0</v>
@@ -9208,52 +9208,52 @@
         <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.1692463751042454</v>
+        <v>-0.3020768159126142</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.003484482547720182</v>
+        <v>0.170806940936108</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.1491519060630798</v>
+        <v>0.1934053789602982</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.04794050336424496</v>
+        <v>-0.2906196403500929</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.07826889449344422</v>
+        <v>0.353709968711982</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.03707318248589899</v>
+        <v>0.1575869518920472</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
         <v>-0</v>
@@ -9265,61 +9265,61 @@
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.1413862299388975</v>
+        <v>-0.267670024023798</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.02372098479200767</v>
+        <v>0.1657468316536151</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.1525670170025926</v>
+        <v>0.2593091775107959</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.1748844742280141</v>
+        <v>-0.2142250703197739</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1349206774462265</v>
+        <v>-0.3625333355198901</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.2717664068154506</v>
+        <v>0.2494367823643885</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.09268929781501452</v>
+        <v>0.100138706777822</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
@@ -9328,16 +9328,16 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02684687466723796</v>
+        <v>-0.08741701757664759</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.1196870373635364</v>
+        <v>0.16399272716267</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>-0</v>
@@ -9346,19 +9346,19 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.08238119961198766</v>
+        <v>-0.2985976867327947</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.07036130047362041</v>
+        <v>0.08122305257699178</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.1570116675471901</v>
+        <v>0.0409759535499578</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
@@ -9367,40 +9367,40 @@
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.09575493682508394</v>
+        <v>-0.1922961089290733</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0555096030494629</v>
+        <v>0.1328098924379702</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.007094972849164682</v>
+        <v>-0.08816248299036697</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.07468524485819628</v>
+        <v>0.1667310992627386</v>
       </c>
       <c r="EQ16" t="n">
         <v>0</v>
@@ -9409,67 +9409,67 @@
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.04777711058161266</v>
+        <v>-0.0107374262169542</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.09114820949941252</v>
+        <v>0.1780235912052323</v>
       </c>
       <c r="EU16" t="n">
         <v>-0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.142186736365141</v>
+        <v>-0.3353759627324941</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.0003621162314809026</v>
+        <v>0.1075312553504576</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.143397138556267</v>
+        <v>0.2271406555925104</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.04533218421797822</v>
+        <v>-0.1935332986380662</v>
       </c>
       <c r="FI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.04791693081151705</v>
+        <v>0.09164464417187074</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.153153298808608</v>
+        <v>0.2278183601319178</v>
       </c>
       <c r="FM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN16" t="n">
         <v>0</v>
@@ -9481,19 +9481,19 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.01105873448072138</v>
+        <v>-0.1456725517972066</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.1996337626910007</v>
+        <v>0.36111669863137</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.2128950060495426</v>
+        <v>-0.1543233162179783</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
@@ -9505,28 +9505,28 @@
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.06678211834370318</v>
+        <v>0.0006198923121755739</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.1473673180968917</v>
+        <v>0.05527164371485965</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
@@ -9537,25 +9537,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3042315980213915</v>
+        <v>0.9245743828721072</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09222312965118104</v>
+        <v>-0.4691675726971176</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.02647625743711347</v>
+        <v>0.1672805927862393</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
         <v>-0</v>
@@ -9564,19 +9564,19 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1938292945710018</v>
+        <v>0.9037560745531809</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1294776390476216</v>
+        <v>-0.6442079991879728</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02783209180400485</v>
+        <v>-0.1125758938652257</v>
       </c>
       <c r="O17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9591,16 +9591,16 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06524821184242191</v>
+        <v>0.1989222270551714</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.001357273267103777</v>
+        <v>-0.1287241873261885</v>
       </c>
       <c r="W17" t="n">
-        <v>0.06220760656112754</v>
+        <v>-0.004600714595648636</v>
       </c>
       <c r="X17" t="n">
         <v>-0</v>
@@ -9609,52 +9609,52 @@
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.05187655279451719</v>
+        <v>0.02803065271143313</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.017084353167277</v>
+        <v>-0.3272729433967189</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.003783994381037783</v>
+        <v>-0.002931812770704408</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.02011604277716852</v>
+        <v>0.2602963135576046</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.06266468335354386</v>
+        <v>-0.08796767914394109</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.0690564829099154</v>
+        <v>0.2709596545208369</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
@@ -9663,28 +9663,28 @@
         <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2153792505580988</v>
+        <v>0.7435873294119582</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.04413373484430763</v>
+        <v>-0.1815033926416931</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.08521650018880855</v>
+        <v>-0.3136121042448002</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>-0</v>
@@ -9696,46 +9696,46 @@
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.03799421830943277</v>
+        <v>-0.06513801403821103</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.1352072694943333</v>
+        <v>-0.1896545316795506</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.08395447143535212</v>
+        <v>0.06256356645669921</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.09963392572900731</v>
+        <v>-0.0219633886687833</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.01058823088306209</v>
+        <v>-0.004824904617835667</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1478218469721866</v>
+        <v>-0.02392570074798646</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
@@ -9750,109 +9750,109 @@
         <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.09158446692407934</v>
+        <v>0.5105194308606337</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.04234839111964196</v>
+        <v>-0.179942370400605</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.06357742990263893</v>
+        <v>-0.1112370494378095</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.05743129112991338</v>
+        <v>-0.3134701133168247</v>
       </c>
       <c r="CF17" t="n">
         <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.002548746422692704</v>
+        <v>0.1628939642285576</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.0136748036576516</v>
+        <v>-0.0580958038735057</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.004414234422143077</v>
+        <v>-0.2198912561875215</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.02759370437029953</v>
+        <v>0.308595786675614</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.07392301267887698</v>
+        <v>0.2209079436430479</v>
       </c>
       <c r="CR17" t="n">
         <v>0</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.04407424362174293</v>
+        <v>-0.3102474117819374</v>
       </c>
       <c r="CX17" t="n">
         <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.01063958854216824</v>
+        <v>0.187613114466148</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.01502916382298097</v>
+        <v>-0.02391059017016119</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.07088220792306847</v>
+        <v>-0.2389628805927723</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.02887410108947309</v>
+        <v>0.1051404327839711</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03207051752015627</v>
+        <v>-0.1384408494795075</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,22 +9885,22 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.02608246595379806</v>
+        <v>-0.2007242168964089</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.08043215122126754</v>
+        <v>-0.05121941068022871</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.0247432571976666</v>
+        <v>0.004985026920643013</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
@@ -9909,25 +9909,25 @@
         <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.07146902420353553</v>
+        <v>-0.1712947365775396</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0311067845748295</v>
+        <v>0.01319602450644088</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.03075689667336226</v>
+        <v>0.06231168274974779</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC17" t="n">
         <v>0</v>
@@ -9936,31 +9936,31 @@
         <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.06056396850589435</v>
+        <v>-0.2361919846803786</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.01501346081531818</v>
+        <v>0.1615348062598025</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.04282358744046035</v>
+        <v>-0.05573502586889351</v>
       </c>
       <c r="EK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
@@ -9969,22 +9969,22 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.01264254954916864</v>
+        <v>0.1551103020235739</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>-0.001713659051987405</v>
+        <v>0.117367508260504</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.04041675272217109</v>
+        <v>0.06199327290302595</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9996,22 +9996,22 @@
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.04684329333929923</v>
+        <v>-0.3535853853140313</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>-0.006485285843273854</v>
+        <v>0.2099121938088286</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.006213811074118563</v>
+        <v>-0.05484633388350661</v>
       </c>
       <c r="FC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,22 +10023,22 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.02436644549754129</v>
+        <v>-0.1086776908867476</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.01811011628927844</v>
+        <v>0.1748484368484225</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.07485745829930321</v>
+        <v>-0.1672962145511032</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
       </c>
       <c r="FM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN17" t="n">
         <v>0</v>
@@ -10047,19 +10047,19 @@
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.05021991950194632</v>
+        <v>-0.3678602691489051</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0605520406172189</v>
+        <v>0.1073477000483014</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.02182204653425179</v>
+        <v>0.1974715160260129</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
@@ -10068,34 +10068,34 @@
         <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.01112507800649763</v>
+        <v>-0.1936421269612184</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.08771260348809326</v>
+        <v>0.1153089829790948</v>
       </c>
       <c r="GC17" t="n">
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
